--- a/data/trans_bre/IP7_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP7_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,71</t>
+          <t>-3,05; 2,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,16</t>
+          <t>-0,83; 5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,19</t>
+          <t>-2,25; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,65</t>
+          <t>-4,37; 3,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 235,64</t>
+          <t>-77,88; 298,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,12; 1237,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,89; 604,27</t>
+          <t>-81,09; 638,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,56; 392,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -0,78</t>
+          <t>-6,89; -0,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,69</t>
+          <t>-1,8; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,2</t>
+          <t>-1,79; 2,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 14,7</t>
+          <t>-0,08; 15,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,4; -7,21</t>
+          <t>-84,47; 1,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 444,39</t>
+          <t>-81,93; 458,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,73; 268,91</t>
+          <t>-69,3; 297,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 1009,95</t>
+          <t>-15,71; 1264,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,08</t>
+          <t>-3,06; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,13</t>
+          <t>-3,73; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,53</t>
+          <t>-4,08; 1,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,36</t>
+          <t>-1,74; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-88,77; 322,1</t>
+          <t>-85,64; 291,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 92,85</t>
+          <t>-70,05; 127,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,25; 120,5</t>
+          <t>-83,99; 129,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,59; 954,13</t>
+          <t>-78,0; 927,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,37</t>
+          <t>-4,54; -0,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,6</t>
+          <t>-3,82; 1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,45</t>
+          <t>-2,21; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,74</t>
+          <t>-5,39; 0,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,03</t>
+          <t>-100,0; 31,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,67; 118,71</t>
+          <t>-77,33; 100,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 683,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,21</t>
+          <t>-100,0; 61,24</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,54</t>
+          <t>-3,23; -0,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,22</t>
+          <t>-1,61; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,02</t>
+          <t>-1,45; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,64</t>
+          <t>-0,98; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,28; -14,75</t>
+          <t>-73,33; -16,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 72,13</t>
+          <t>-49,94; 55,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 70,58</t>
+          <t>-54,2; 63,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 201,16</t>
+          <t>-37,29; 216,36</t>
         </is>
       </c>
     </row>
